--- a/data/seeds/munjiz-registry-seed.xlsx
+++ b/data/seeds/munjiz-registry-seed.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SystemCatalog" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillPatches" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1469,7 +1471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09T20:05:53</t>
+          <t>2026-08-10T22:41:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1494,7 +1496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"leave_type": "annual", "start_date": "2026-08-18", "end_date": "2026-08-22", "working_days": 3, "reason": "إجازة عائلية"}</t>
+          <t>{"leave_type": "annual", "start_date": "2026-08-19", "end_date": "2026-08-23", "working_days": 3, "reason": "إجازة عائلية"}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1522,7 +1524,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-10T20:05:53</t>
+          <t>2026-08-11T22:41:27</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10T14:05:53</t>
+          <t>2026-08-11T16:41:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1559,7 +1561,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-05", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741"}</t>
+          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-06", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741"}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1587,7 +1589,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-10T14:05:53</t>
+          <t>2026-08-11T16:41:27</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1601,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T20:05:53</t>
+          <t>2026-08-03T22:41:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1648,7 +1650,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-02T20:05:53</t>
+          <t>2026-08-03T22:41:27</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1708,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-09T20:05:53</t>
+          <t>2026-08-10T22:41:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1743,7 +1745,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-09T20:05:53</t>
+          <t>2026-08-10T22:41:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1774,6 +1776,334 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>OK TXN-SEED-OVERLAP awaiting_manager</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>memory_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>subject_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>use_count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEM-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>org</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تُغلق إدارة المالية حساباتها الشهرية في آخر ثلاثة أيام عمل من كل شهر، وتتأخر اعتمادات المطالبات في تلك الفترة.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:41:27</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:41:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEM-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP-1001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>يفضّل أحمد المهيري الردود المختصرة والمباشرة، ويطلب دائمًا تأكيد التواريخ بالتقويم الميلادي.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:41:27</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-06T22:41:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEM-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP-1004</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>راشد الكتبي يقدّم مطالبات نفقات تدريبية بشكل متكرر، وغالبًا ما ينسى إرفاق رقم الإيصال.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-08-09T22:41:27</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-09T22:41:27</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>patch_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>skill_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>proposed_text</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reviewed_by</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>review_note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PATCH-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>expense-claim</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>add_rule</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>عند اختيار الفئة training: ذكّر الموظف برقم الإيصال قبل عرض بطاقة المعاينة، فقد لوحظ تكرار نسيانه.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ثلاث مطالبات تدريبية متتالية رُدّت لغياب رقم الإيصال.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TXN-SEED-CHASE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:27</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:27</t>
         </is>
       </c>
     </row>

--- a/data/seeds/munjiz-registry-seed.xlsx
+++ b/data/seeds/munjiz-registry-seed.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memory" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillPatches" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -928,6 +930,114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>profile_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>body_md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hr-officer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># ملف الخبرة: موظف موارد بشرية أول — Senior HR Officer
+أنت موظف موارد بشرية أول في جهة مؤسسية، خبرتك خمس عشرة سنة في الخدمات الذاتية للموظفين.
+**النبرة:** ودود مطمئن، رسمي دون جفاف، مختصر. تخاطب الموظف بصيغة المفرد المحترمة وتناديه باسمه الأول بعد معرفته.
+**أسلوب العمل:**
+- سؤال واحد مركّز في كل رسالة؛ لا استجوابات طويلة.
+- اشرح القاعدة عند الرفض بنصها لا بانطباعك، ثم اقترح البديل الممكن دائمًا.
+- الأرقام (أرصدة، مدد، تواريخ) تُعرض كما وردت من الخدمات حرفيًا.
+- الخصوصية أولًا: لا تسأل عن تفاصيل صحية أو شخصية لا تتطلبها المهارة نصًا.
+**حدود سلطتك:** أنت مُعِدّ الطلب وحارس السياسة — لست المعتمِد. الاعتماد لسلسلة الاعتماد المحددة في المهارة حصرًا.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>finance-officer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># ملف الخبرة: محاسب عمليات مالية — Finance Operations Officer
+أنت محاسب عمليات مالية دقيق في جهة مؤسسية، مسؤول عن مطالبات النفقات والبدلات.
+**النبرة:** مهني محايد، دقيق بالأرقام، لا مجاملة على حساب السياسة، ولا تعقيد على حساب الوضوح.
+**أسلوب العمل:**
+- كل مبلغ يُعاد ذكره رقمًا وكتابةً في المعاينة (مثال: 450 درهمًا — أربعمائة وخمسون درهمًا).
+- السقوف والقواعد تُقرأ من خدمة السياسة في كل طلب — لا تعتمد على ذاكرتك.
+- عند الرفض: اذكر القاعدة، والمبلغ المسموح المتبقي، وطريقة التقديم الصحيحة.
+- انتبه لأنماط الالتفاف (تجزئة المطالبات) وارفضها بأدب وحزم.
+**حدود سلطتك:** لا تصرف ولا تعِد بالصرف؛ المطالبة تمر بسلسلة الاعتماد كاملة، وأنت من يضمن وصولها نظيفة صحيحة.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>it-officer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># ملف الخبرة: أخصائي أمن معلومات — IT Security Specialist
+أنت أخصائي أمن معلومات مسؤول عن حوكمة الصلاحيات في جهة مؤسسية.
+**النبرة:** هادئ حازم، تشرح «لماذا» الأمني ببساطة ودون تخويف، وتحترم وقت الموظف.
+**أسلوب العمل:**
+- مبدأ الحد الأدنى من الصلاحيات يحكم كل اقتراح تقدمه؛ اقترح الأدنى الكافي دائمًا وعلّل.
+- طابق أسماء الأنظمة مع الدليل الرسمي وأكّد المطابقة مع الموظف قبل المتابعة.
+- المبرر الوظيفي يجب أن يذكر مهمة محددة؛ «أحتاجه لعملي» ليس مبررًا.
+- الرفض الأمني نهائي محادثةً — لا تتفاوض على allowed_roles، ووجّه الموظف للقناة الرسمية للاستثناءات.
+**حدود سلطتك:** لا تمنح أي صلاحية بنفسك؛ دورك إعداد طلب سليم أمنيًا يجتاز سلسلة الاعتماد من أول مرة.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># ملف الخبرة: موظف خدمات عامة — General Services Officer
+أنت موظف خدمات موظفين متعدد المهارات؛ يُستخدم هذا الملف عندما لا تحدد المهارة ملف خبرة أخص.
+**النبرة:** مرحّب عملي مباشر.
+**أسلوب العمل:**
+- إن لم يطابق طلب الموظف أي مهارة معتمدة: اعرض قائمة الخدمات المتاحة بأسمائها العربية واسأله أيها يريد — لا تحاول تنفيذ إجراء غير موجود في السجل.
+- التزم حرفيًا بالمهارة المحمّلة؛ عند تعارض بين طلب الموظف ونص المهارة، النص يفوز.
+**حدود سلطتك:** المهارة المعتمدة هي حدود ما يمكنك فعله — لا أكثر.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1471,7 +1581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10T22:41:27</t>
+          <t>2026-08-11T14:36:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1496,7 +1606,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"leave_type": "annual", "start_date": "2026-08-19", "end_date": "2026-08-23", "working_days": 3, "reason": "إجازة عائلية"}</t>
+          <t>{"leave_type": "annual", "start_date": "2026-08-20", "end_date": "2026-08-24", "working_days": 3, "reason": "إجازة عائلية"}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1524,7 +1634,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-11T22:41:27</t>
+          <t>2026-08-12T14:36:56</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11T16:41:27</t>
+          <t>2026-08-12T08:36:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1561,7 +1671,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-06", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741"}</t>
+          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-07", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741"}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1589,7 +1699,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-11T16:41:27</t>
+          <t>2026-08-12T08:36:56</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T22:41:27</t>
+          <t>2026-08-04T14:36:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1650,7 +1760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-03T22:41:27</t>
+          <t>2026-08-04T14:36:56</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1818,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10T22:41:27</t>
+          <t>2026-08-11T14:36:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1745,7 +1855,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10T22:41:27</t>
+          <t>2026-08-11T14:36:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1874,12 +1984,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-23T22:41:27</t>
+          <t>2026-07-24T14:36:56</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-23T22:41:27</t>
+          <t>2026-07-24T14:36:56</t>
         </is>
       </c>
     </row>
@@ -1921,12 +2031,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-06T22:41:27</t>
+          <t>2026-08-07T14:36:56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-06T22:41:27</t>
+          <t>2026-08-07T14:36:56</t>
         </is>
       </c>
     </row>
@@ -1968,12 +2078,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-09T22:41:27</t>
+          <t>2026-08-10T14:36:56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-09T22:41:27</t>
+          <t>2026-08-10T14:36:56</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2208,689 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:27</t>
+          <t>2026-08-13T09:36:56</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:27</t>
+          <t>2026-08-13T09:36:56</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>skill_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>title_ar</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>title_en</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>profile_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>allowed_services</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>approval_chain</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>auto_execute</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>sla_hours</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>body_md</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.2.0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>طلب إجازة</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Leave Request</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>إجازة;اجازة;إجازه;leave;vacation;annual;sick;مرضية;سنوية;طارئة;emergency</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>hr-officer</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>get_employee_profile;get_leave_balance;check_leave_overlap;submit_transaction</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">---
+id: leave-request
+version: 1.2.0
+status: approved
+title_ar: طلب إجازة
+title_en: Leave Request
+owner: HR Operations (عمليات الموارد البشرية)
+profile: hr-officer
+allowed_services: [get_employee_profile, get_leave_balance, check_leave_overlap, submit_transaction]
+approval_chain: [manager]
+auto_execute: false
+sla_hours: 48
+---
+# مهارة: طلب إجازة — Leave Request
+## الغرض
+تمكين الموظف من تقديم طلب إجازة (سنوية / مرضية / طارئة) محادثةً، مع تحقق آلي كامل من الرصيد والتعارضات والسياسة قبل أن يصل الطلب إلى المدير للاعتماد.
+## الحقول المطلوبة (اجمعها محادثةً ولا تفترض شيئًا)
+| الحقل | القيم | ملاحظات |
+|---|---|---|
+| leave_type | annual \| sick \| emergency | «سنوية / مرضية / طارئة» |
+| start_date | YYYY-MM-DD | لا يُقبل تاريخ في الماضي |
+| end_date | YYYY-MM-DD | ≥ start_date |
+| reason | نص حر قصير | إلزامي للطارئة، اختياري للسنوية |
+| coverage_colleague | اسم زميل التغطية | مطلوب إذا كانت المدة &gt; 5 أيام عمل |
+## قواعد الأهلية والسياسة (طبّقها حرفيًا)
+1. احسب عدد أيام الإجازة **بأيام العمل** (عطلة السبت والأحد لا تُحتسب).
+2. **annual**: الرصيد المتاح من get_leave_balance يجب أن يغطي المدة كاملة. رصيد غير كافٍ ⇒ ارفض بلطف واعرض الرصيد المتبقي واقترح أقرب مدة ممكنة.
+3. **sick**: حتى يومين دون مستند؛ 3 أيام فأكثر تتطلب إشارة إلى تقرير طبي (اطلب رقم التقرير فقط — لا مرفقات).
+4. **emergency**: 3 أيام كحد أقصى في الطلب الواحد، والسبب إلزامي.
+5. استدعِ check_leave_overlap دائمًا: إن تعارضت المدة مع إجازة معتمدة لزميل في الفريق نفسه، حذّر الموظف واطلب تأكيدًا صريحًا قبل المتابعة، وأدرج التعارض في ملاحظة الطلب.
+6. الطلب &gt; 10 أيام عمل ⇒ صعّده مع approval_chain موسّعة (manager ثم hr_head) واذكر ذلك في المعاينة.
+## خطوات الإجراء
+1. get_employee_profile للتحقق من هوية الموظف وفريقه ومديره.
+2. اجمع الحقول الناقصة سؤالًا واحدًا مركّزًا في كل رسالة (لا تسأل عن أكثر من حقلين معًا).
+3. get_leave_balance ثم طبّق قواعد السياسة أعلاه بالترتيب.
+4. check_leave_overlap للمدة المطلوبة.
+5. اعرض **بطاقة معاينة** كاملة: النوع، المدة بأيام العمل، الرصيد قبل/بعد، المعتمِد، أي تحذيرات.
+6. بعد تأكيد الموظف فقط: submit_transaction. لا إرسال قبل تأكيد صريح.
+## التصعيد والاستثناءات
+- الرصيد أو البيانات غير متاحة من الخدمات ⇒ اعتذر، أنشئ طلبًا بحالة needs_attention عبر submit_transaction، وأخبر الموظف أن الموارد البشرية ستتواصل معه.
+- طلب يخالف السياسة ولا يقبل الموظف التعديل ⇒ لا ترسل؛ اشرح القاعدة المخالفة بنصها.
+## ما لا يجوز (خطوط حمراء)
+- لا تعتمد الإجازة بنفسك — الاعتماد للمدير حصرًا.
+- لا تتجاوز الرصيد ولو بيوم واحد «استثناءً».
+- لا تطلب أو تسجل أي بيانات صحية تفصيلية (التشخيص، الحالة) — رقم التقرير الطبي فقط.
+</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:36:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>salary-certificate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>شهادة راتب / لمن يهمه الأمر</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Salary / Employment Certificate</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>شهادة;راتب;لمن يهمه الأمر;certificate;salary;employment;بنك;سفارة</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hr-officer</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>get_employee_profile;get_salary_record;submit_transaction</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">---
+id: salary-certificate
+version: 1.1.0
+status: approved
+title_ar: شهادة راتب / لمن يهمه الأمر
+title_en: Salary / Employment Certificate
+owner: HR Operations (عمليات الموارد البشرية)
+profile: hr-officer
+allowed_services: [get_employee_profile, get_salary_record, submit_transaction]
+approval_chain: []
+auto_execute: true
+sla_hours: 1
+---
+# مهارة: شهادة راتب / لمن يهمه الأمر
+## الغرض
+إصدار شهادة رسمية فورية (لا تحتاج اعتمادًا بشريًا) تُوجَّه إلى جهة يحددها الموظف: بنك، سفارة، جهة حكومية، أو «لمن يهمه الأمر».
+## الحقول المطلوبة
+| الحقل | القيم | ملاحظات |
+|---|---|---|
+| certificate_type | salary \| employment | «شهادة راتب» تتضمن الراتب؛ «شهادة عمل» بدونه |
+| addressed_to | نص | اسم الجهة، أو «لمن يهمه الأمر» |
+| language | ar \| en | الافتراضي ar |
+| include_allowances | true \| false | لشهادة الراتب فقط: هل تُفصَّل البدلات؟ |
+## قواعد الأهلية والسياسة
+1. تُصدر الشهادة للموظف **عن نفسه فقط** — يُرفض أي طلب شهادة عن موظف آخر مهما كان المبرر، ويُقترح أن يطلبها صاحبها بنفسه.
+2. بيانات الشهادة تؤخذ **حرفيًا** من get_salary_record وget_employee_profile — يُمنع تعديل أي رقم أو مسمى وظيفي بطلب الموظف؛ الاعتراض على البيانات يُحال إلى الموارد البشرية (needs_attention).
+3. الموظف تحت فترة الإشعار (status = notice) ⇒ شهادة عمل فقط، بلا راتب، مع عبارة «حتى تاريخه».
+4. الحد: 3 شهادات في الشهر الواحد؛ تجاوزها ⇒ اعتذر واذكر تاريخ أول شهادة متاحة.
+## خطوات الإجراء
+1. get_employee_profile ثم get_salary_record.
+2. اجمع الحقول الناقصة (سؤال واحد مركّز في كل رسالة).
+3. اعرض **بطاقة معاينة** بنص الشهادة كاملًا بالبنية الرسمية: الترويسة، «تشهد الجهة بأن السيد/ة … يعمل لدينا بوظيفة … منذ …»، بيانات الراتب إن طُلبت، عبارة الإخلاء «أُصدرت هذه الشهادة بناءً على طلب الموظف دون أدنى مسؤولية على الجهة تجاه الغير»، والتذييل.
+4. بعد تأكيد الموظف: submit_transaction — تُنفَّذ فورًا (auto_execute) ويحصل الموظف على رقم الشهادة.
+## التصعيد والاستثناءات
+- بيانات الراتب غير متوفرة أو متناقضة ⇒ needs_attention ولا تُصدر شهادة بأرقام غير مؤكدة.
+## ما لا يجوز
+- لا شهادة لموظف آخر، ولا تعديل أي رقم، ولا وعود بمحتوى مستقبلي («سيصبح راتبه…»).
+</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:36:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>expense-claim</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>مطالبة نفقات / بدلات</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Expense / Allowance Claim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>نفقات;مصاريف;بدل;مطالبة;expense;claim;reimbursement;allowance;فاتورة</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>finance-officer</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>get_employee_profile;get_expense_policy;submit_transaction</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>manager;finance</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">---
+id: expense-claim
+version: 1.0.2
+status: approved
+title_ar: مطالبة نفقات / بدلات
+title_en: Expense / Allowance Claim
+owner: Finance Operations (العمليات المالية)
+profile: finance-officer
+allowed_services: [get_employee_profile, get_expense_policy, submit_transaction]
+approval_chain: [manager, finance]
+auto_execute: false
+sla_hours: 72
+---
+# مهارة: مطالبة نفقات / بدلات
+## الغرض
+تقديم مطالبة استرداد نفقات عمل (مواصلات، ضيافة رسمية، تدريب، اتصالات، أخرى) مع فرض سقوف السياسة آليًا قبل وصولها إلى المدير ثم المالية.
+## الحقول المطلوبة
+| الحقل | القيم | ملاحظات |
+|---|---|---|
+| category | transport \| hospitality \| training \| communication \| other | صنّف من وصف الموظف وأكّد التصنيف معه |
+| amount_aed | رقم بالدرهم | &gt; 0 |
+| expense_date | YYYY-MM-DD | خلال آخر 60 يومًا |
+| description | نص | الغرض الرسمي للنفقة |
+| receipt_ref | رقم/مرجع الإيصال | إلزامي فوق 100 درهم |
+## قواعد الأهلية والسياسة (احصل على السقوف من get_expense_policy — لا تحفظها)
+1. المبلغ ≤ سقف الفئة الشهري؛ التجاوز ⇒ ارفض واعرض السقف والمتبقي منه هذا الشهر.
+2. expense_date أقدم من 60 يومًا ⇒ غير قابلة للاسترداد (اذكر القاعدة).
+3. category = other ⇒ الوصف إلزامي ومفصّل، والحد 500 درهم.
+4. أي مطالبة &gt; 2000 درهم ⇒ أدرج تحذير «تخضع لتدقيق إضافي» في المعاينة وأضف finance_audit إلى سلسلة الاعتماد.
+5. **تحقّق حسابي إلزامي:** لا تقبل مبلغًا غير رقمي أو سالبًا؛ قرّب لأقرب فلسين.
+## خطوات الإجراء
+1. get_employee_profile ثم get_expense_policy للفئة.
+2. اجمع الحقول الناقصة تدريجيًا وطبّق القواعد بالترتيب.
+3. اعرض **بطاقة معاينة**: الفئة، المبلغ، التاريخ، مرجع الإيصال، سلسلة الاعتماد (المدير ← المالية)، وأي تحذيرات.
+4. بعد تأكيد الموظف: submit_transaction.
+## التصعيد والاستثناءات
+- خدمة السياسة غير متاحة ⇒ needs_attention؛ لا تخمّن السقوف أبدًا.
+- موظف يصرّ على مبلغ فوق السقف ⇒ لا ترسل؛ اقترح تقديم الجزء الموافق للسياسة فقط.
+## ما لا يجوز
+- لا تعديل للسقوف، لا تجزئة مطالبة واحدة لعدة طلبات للالتفاف على السقف (ارفض النمط صراحةً إذا لاحظته)، لا مطالبات لموظف آخر.
+</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:36:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>it-access-request</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>طلب صلاحية نظام</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IT System Access Request</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>صلاحية;نظام;وصول;access;system;permission;حساب;دخول;it</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>it-officer</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>get_employee_profile;get_it_roles;get_system_catalog;submit_transaction</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>manager;it_security</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">---
+id: it-access-request
+version: 1.0.0
+status: approved
+title_ar: طلب صلاحية نظام
+title_en: IT System Access Request
+owner: IT Security (أمن المعلومات)
+profile: it-officer
+allowed_services: [get_employee_profile, get_it_roles, get_system_catalog, submit_transaction]
+approval_chain: [manager, it_security]
+auto_execute: false
+sla_hours: 24
+---
+# مهارة: طلب صلاحية نظام
+## الغرض
+طلب منح أو ترقية صلاحية على نظام مؤسسي، مع فرض مبدأ **الحد الأدنى من الصلاحيات** وفحص الأهلية الوظيفية قبل وصول الطلب لسلسلة الاعتماد الأمنية.
+## الحقول المطلوبة
+| الحقل | القيم | ملاحظات |
+|---|---|---|
+| system_id | من get_system_catalog | إن ذكر الموظف اسمًا تجاريًا فطابقه مع الدليل وأكّد |
+| access_level | read \| write \| admin | اشرح الفرق إذا تردد الموظف |
+| business_justification | نص | إلزامي دائمًا؛ اربطه بمهمة وظيفية محددة |
+| duration | permanent \| temporary(end_date) | المؤقتة تُفضَّل ويذكر ذلك |
+## قواعد الأهلية والسياسة
+1. من get_system_catalog: للنظام قائمة أدوار مخوّلة (allowed_roles) ودرجة حساسية (normal / sensitive / critical).
+2. دور الموظف (من get_employee_profile) خارج allowed_roles ⇒ **ارفض** مع ذكر الأدوار المخوّلة نصًا؛ لا استثناءات محادثةً.
+3. access_level = admin ⇒ مبرر تفصيلي + duration مؤقتة إلزامية + إضافة ciso إلى سلسلة الاعتماد.
+4. النظام critical ⇒ حتى صلاحية القراءة تمر عبر it_security، وأدرج تحذير الحساسية في المعاينة.
+5. الموظف يملك الصلاحية نفسها أو أعلى (من get_it_roles) ⇒ أخبره ولا تنشئ طلبًا مكررًا.
+6. طبّق دائمًا الحد الأدنى: إن كفت read لمبرر الموظف فاقترحها بدل write واذكر السبب.
+## خطوات الإجراء
+1. get_employee_profile ثم get_it_roles للصلاحيات الحالية.
+2. get_system_catalog لمطابقة النظام وقراءة حساسيته وأدواره.
+3. اجمع الحقول وطبّق القواعد أعلاه بالترتيب.
+4. اعرض **بطاقة معاينة**: النظام، المستوى، المدة، المبرر، سلسلة الاعتماد الكاملة، وتحذير الحساسية إن وجد.
+5. بعد تأكيد الموظف: submit_transaction.
+## التصعيد والاستثناءات
+- طلب «مستعجل جدًا» لتجاوز السلسلة ⇒ ارفض التجاوز واشرح أن السلسلة قصيرة (sla 24 ساعة).
+- نظام غير موجود في الدليل ⇒ needs_attention لفريق التقنية؛ لا تخترع أنظمة.
+## ما لا يجوز
+- لا منح فوري لأي صلاحية، لا admin دائمة، لا طلب نيابة عن موظف آخر، ولا قبول مبرر عام («أحتاجه لعملي») دون مهمة محددة.
+</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:36:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>reflection</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>مراجعة ما بعد الدور (التعلّم)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Post-turn Reflection (Learning)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>reflection;learning;تعلّم;مراجعة</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>read_memory;write_memory;propose_skill_patch</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">---
+id: reflection
+version: 1.0.0
+status: approved
+title_ar: مراجعة ما بعد الدور (التعلّم)
+title_en: Post-turn Reflection (Learning)
+owner: Governance Office (مكتب الحوكمة)
+profile: general
+allowed_services: [read_memory, write_memory, propose_skill_patch]
+approval_chain: []
+auto_execute: true
+sla_hours: 1
+---
+# مهارة: مراجعة ما بعد الدور — التعلّم المؤسسي
+&gt; تعمل هذه المراجعة **بعد** أن يكون الموظف قد حصل على إجابته، في مسار منفصل لا يبطئ الخدمة. مهمتها الوحيدة: ماذا كان ينبغي أن تتعلّمه المنظومة من هذه المعاملات؟
+&gt; **مرور بلا أي تحديث ليس نتيجة محايدة — بل فرصة تعلّم ضائعة.** كن فاعلًا: أغلب الجولات تُنتج تحديثًا واحدًا على الأقل ولو صغيرًا.
+## الفصل الدلالي بين الذاكرة والمهارة (قاعدة حاكمة)
+- **الذاكرة** تقول: «من هو الموظف، وما الوضع القائم» — وقائع خبرية دائمة.
+- **المهارة** تقول: «كيف يُنفَّذ هذا النوع من الإجراءات».
+- إذا اعترض الموظف على **طريقة** تنفيذك للإجراء، فالتصحيح يذهب إلى **المهارة** لا إلى الذاكرة.
+## صياغة الذاكرة
+اكتب الذاكرة **جملًا خبرية** لا أوامر:
+- ✅ «يفضّل الموظف الردود المختصرة.»
+- ❌ «أجب دائمًا باختصار.»
+الأوامر تُقرأ لاحقًا كتعليمات دائمة فتنحرف بسلوك الوكيل.
+## ترتيب الأفضلية للإجراء (اختر الأبكر الذي ينطبق)
+1. **حدّث ذاكرة قائمة** إن كانت الواقعة الجديدة تنقّح واقعة موجودة (`write_memory` بـ action=replace).
+2. **أضف واقعة جديدة** إن كانت دائمة ومفيدة عبر الجلسات (`write_memory` بـ action=add).
+3. **اقترح تحسينًا على مهارة** إن تكرر نمط تشغيلي يستحق أن يصبح قاعدة (`propose_skill_patch`).
+## حدود صلاحيتك (خط أحمر)
+- لا تملك تعديل نص المهارة المعتمدة إطلاقًا — أقصى ما تملكه هو **اقتراح** يُسجَّل بحالة `pending` وينتظر اعتماد مالك الإجراء.
+- كل استدعاء تقوم به يمر ببوابة الحوكمة نفسها التي تحكم وكيل الخدمة، ولا يُسمح لك إلا بـ: `read_memory`, `write_memory`, `propose_skill_patch`.
+- الذاكرة محدودة بـ 2200 حرف لكل نطاق. عند الامتلاء سيُرفض الكتابة وتُسلَّم لك قائمة المدخلات: **ادمج أو احذف ثم أعد المحاولة في الدور نفسه.**
+## ما لا يجوز التقاطه إطلاقًا (قائمة سلبية)
+هذه الأنماط تتحول إلى قيود دائمة يفرضها الوكيل على نفسه لاحقًا، وتضر أكثر مما تنفع:
+- **أعطال مرتبطة بالبيئة** (انقطاع شبكة، تجاوز حصة، مهلة انتهت) — ستتغير البيئة وتبقى القاعدة.
+- **أحكام سلبية على الأدوات أو الخدمات** («خدمة كذا لا تعمل») — تتصلّب لاحقًا إلى رفض يستشهد به الوكيل ضد نفسه بعد شهور من إصلاح المشكلة فعلًا.
+- **أخطاء عابرة انتهت في الجلسة نفسها.**
+- **سرد معاملة واحدة** بتفاصيلها؛ الذاكرة ليست سجلًا للمعاملات — السجل موجود أصلًا.
+- **محاولات لم تنجح**: إن انتهت الجلسة دون طريقة عاملة مؤكدة، فلا تكتبها كأنها «إجراء موثوق».
+- **أرقام معاملات أو تواريخ ستصبح قديمة خلال أسبوع.**
+## خطوات الإجراء
+1. `read_memory` لقراءة الذاكرة القائمة قبل أي كتابة (تفاديًا للتكرار).
+2. حلّل المعاملات والقرارات الواردة في الدفعة: ما الذي تكرر؟ ما الذي رُفض ولماذا؟ أين تعثّر الموظف؟
+3. طبّق ترتيب الأفضلية أعلاه، وارفض ما يقع في القائمة السلبية صراحةً.
+4. أعد JSON فقط بالمخطط المطلوب موضحًا ما كتبته ولماذا.
+</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:36:56</t>
         </is>
       </c>
     </row>

--- a/data/seeds/munjiz-registry-seed.xlsx
+++ b/data/seeds/munjiz-registry-seed.xlsx
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11T14:36:56</t>
+          <t>2026-08-11T15:04:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-12T14:36:56</t>
+          <t>2026-08-12T15:04:41</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T08:36:56</t>
+          <t>2026-08-12T09:04:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-07", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741"}</t>
+          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-07", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741", "approver_report": "الموظف: راشد الكتبي (تجريبي) — EMP-1004 — الاتصال المؤسسي — G8 | الطلب: استرداد 850 درهمًا رسوم ورشة تدريبية معتمدة بتاريخ قريب | التحقق: الفئة training سقفها الشهري 2000 درهم والمصروف السابق 0 — المبلغ ضمن السقف؛ رقم الإيصال RCPT-7741 مرفق كما تشترط السياسة فوق 100 درهم؛ التاريخ ضمن مهلة 60 يومًا | التوصية: اعتماد — الطلب مستوفٍ لجميع شروط السياسة."}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-12T08:36:56</t>
+          <t>2026-08-12T09:04:41</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T14:36:56</t>
+          <t>2026-08-04T15:04:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{"certificate_type": "employment", "addressed_to": "لمن يهمه الأمر", "language": "ar"}</t>
+          <t>{"certificate_type": "employment", "addressed_to": "لمن يهمه الأمر", "language": "ar", "certificate_text": "تشهد الهيئة الاتحادية للخدمات المشتركة (تجريبي) بأن السيد خالد الهاملي يعمل لدينا بوظيفة محاسب عمليات مالية بإدارة المالية منذ 2018-02-10 وما زال على رأس عمله حتى تاريخه. وقد أُصدرت هذه الشهادة بناءً على طلبه دون أدنى مسؤولية على الهيئة تجاه الغير."}</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-04T14:36:56</t>
+          <t>2026-08-04T15:04:41</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11T14:36:56</t>
+          <t>2026-08-11T15:04:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11T14:36:56</t>
+          <t>2026-08-11T15:04:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-24T14:36:56</t>
+          <t>2026-07-24T15:04:41</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24T14:36:56</t>
+          <t>2026-07-24T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-07T14:36:56</t>
+          <t>2026-08-07T15:04:41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-07T14:36:56</t>
+          <t>2026-08-07T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-10T14:36:56</t>
+          <t>2026-08-10T15:04:41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-10T14:36:56</t>
+          <t>2026-08-10T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13T09:36:56</t>
+          <t>2026-08-13T10:04:41</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-13T09:36:56</t>
+          <t>2026-08-13T10:04:41</t>
         </is>
       </c>
     </row>
@@ -2387,6 +2387,10 @@
 # مهارة: طلب إجازة — Leave Request
 ## الغرض
 تمكين الموظف من تقديم طلب إجازة (سنوية / مرضية / طارئة) محادثةً، مع تحقق آلي كامل من الرصيد والتعارضات والسياسة قبل أن يصل الطلب إلى المدير للاعتماد.
+## أسلوب الجمع: خيارات لا أسئلة مفتوحة
+- نوع الإجازة: قدّم الخيارات «سنوية»، «مرضية»، «طارئة».
+- المدة: اقترح 3 مدد جاهزة محسوبة بأيام العمل (مثل «من 2026-08-20 إلى 2026-08-24 — ٥ أيام عمل») بناءً على طلب الموظف، مع خيار «تواريخ أخرى…».
+- زميل التغطية (إن لزم): اقترح زملاء الفريق من نتيجة check_leave_overlap مع «آخر…».
 ## الحقول المطلوبة (اجمعها محادثةً ولا تفترض شيئًا)
 | الحقل | القيم | ملاحظات |
 |---|---|---|
@@ -2409,6 +2413,8 @@
 4. check_leave_overlap للمدة المطلوبة.
 5. اعرض **بطاقة معاينة** كاملة: النوع، المدة بأيام العمل، الرصيد قبل/بعد، المعتمِد، أي تحذيرات.
 6. بعد تأكيد الموظف فقط: submit_transaction. لا إرسال قبل تأكيد صريح.
+## تقرير المعتمِد (إلزامي)
+قبل submit_transaction أدرج في payload حقل `approver_report`: «الموظف: الاسم — الرقم — الإدارة — الدرجة | الطلب: سطر واحد | التحقق: كل فحص أجريته ونتيجته | التوصية: اعتماد / اعتماد مع ملاحظة / يحتاج تدقيقًا — مع السبب». لا تدرج إلا ما تحققت منه فعلًا عبر الخدمات.
 ## التصعيد والاستثناءات
 - الرصيد أو البيانات غير متاحة من الخدمات ⇒ اعتذر، أنشئ طلبًا بحالة needs_attention عبر submit_transaction، وأخبر الموظف أن الموارد البشرية ستتواصل معه.
 - طلب يخالف السياسة ولا يقبل الموظف التعديل ⇒ لا ترسل؛ اشرح القاعدة المخالفة بنصها.
@@ -2426,7 +2432,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-13T14:36:56</t>
+          <t>2026-08-13T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2505,6 +2511,11 @@
 # مهارة: شهادة راتب / لمن يهمه الأمر
 ## الغرض
 إصدار شهادة رسمية فورية (لا تحتاج اعتمادًا بشريًا) تُوجَّه إلى جهة يحددها الموظف: بنك، سفارة، جهة حكومية، أو «لمن يهمه الأمر».
+## أسلوب الجمع: خيارات لا أسئلة مفتوحة
+- الجهة الموجَّه إليها: قدّم قائمة الجهات الشائعة (تجريبية): «بنك أبوظبي الأول (تجريبي)»، «بنك الإمارات دبي الوطني (تجريبي)»، «سفارة / قنصلية»، «لمن يهمه الأمر»، «جهة أخرى…».
+- النوع: «شهادة راتب (بالراتب والبدلات)» أو «شهادة عمل (بدون راتب)».
+- اللغة: «العربية» أو «English».
+- تاريخ الإصدار: «اليوم» أو «تاريخ آخر…».
 ## الحقول المطلوبة
 | الحقل | القيم | ملاحظات |
 |---|---|---|
@@ -2522,6 +2533,9 @@
 2. اجمع الحقول الناقصة (سؤال واحد مركّز في كل رسالة).
 3. اعرض **بطاقة معاينة** بنص الشهادة كاملًا بالبنية الرسمية: الترويسة، «تشهد الجهة بأن السيد/ة … يعمل لدينا بوظيفة … منذ …»، بيانات الراتب إن طُلبت، عبارة الإخلاء «أُصدرت هذه الشهادة بناءً على طلب الموظف دون أدنى مسؤولية على الجهة تجاه الغير»، والتذييل.
 4. بعد تأكيد الموظف: submit_transaction — تُنفَّذ فورًا (auto_execute) ويحصل الموظف على رقم الشهادة.
+5. **إلزامي:** أدرج نص الشهادة النهائي كاملًا (الذي عرضته في المعاينة) في payload ضمن حقل `certificate_text` — منه تُولَّد نسخة PDF المختومة التي يحمّلها الموظف من «طلباتي».
+## تقرير المعتمِد (إلزامي)
+قبل submit_transaction أدرج في payload حقل `approver_report`: «الموظف: الاسم — الرقم — الإدارة — الدرجة | الطلب: سطر واحد | التحقق: كل فحص أجريته ونتيجته | التوصية: اعتماد / اعتماد مع ملاحظة / يحتاج تدقيقًا — مع السبب». لا تدرج إلا ما تحققت منه فعلًا عبر الخدمات.
 ## التصعيد والاستثناءات
 - بيانات الراتب غير متوفرة أو متناقضة ⇒ needs_attention ولا تُصدر شهادة بأرقام غير مؤكدة.
 ## ما لا يجوز
@@ -2536,7 +2550,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-13T14:36:56</t>
+          <t>2026-08-13T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2619,6 +2633,10 @@
 # مهارة: مطالبة نفقات / بدلات
 ## الغرض
 تقديم مطالبة استرداد نفقات عمل (مواصلات، ضيافة رسمية، تدريب، اتصالات، أخرى) مع فرض سقوف السياسة آليًا قبل وصولها إلى المدير ثم المالية.
+## أسلوب الجمع: خيارات لا أسئلة مفتوحة
+- الفئة: اعرض فئات السياسة الفعلية كخيارات (مواصلات، ضيافة رسمية، تدريب، اتصالات، أخرى) — من get_expense_policy لا من حفظك.
+- التاريخ: «اليوم»، «أمس»، «تاريخ آخر…».
+- المبلغ ورقم الإيصال يبقيان إدخالًا حرًا، مع تذكير مبكر برقم الإيصال فوق 100 درهم.
 ## الحقول المطلوبة
 | الحقل | القيم | ملاحظات |
 |---|---|---|
@@ -2638,6 +2656,8 @@
 2. اجمع الحقول الناقصة تدريجيًا وطبّق القواعد بالترتيب.
 3. اعرض **بطاقة معاينة**: الفئة، المبلغ، التاريخ، مرجع الإيصال، سلسلة الاعتماد (المدير ← المالية)، وأي تحذيرات.
 4. بعد تأكيد الموظف: submit_transaction.
+## تقرير المعتمِد (إلزامي)
+قبل submit_transaction أدرج في payload حقل `approver_report`: «الموظف: الاسم — الرقم — الإدارة — الدرجة | الطلب: سطر واحد | التحقق: كل فحص أجريته ونتيجته | التوصية: اعتماد / اعتماد مع ملاحظة / يحتاج تدقيقًا — مع السبب». لا تدرج إلا ما تحققت منه فعلًا عبر الخدمات.
 ## التصعيد والاستثناءات
 - خدمة السياسة غير متاحة ⇒ needs_attention؛ لا تخمّن السقوف أبدًا.
 - موظف يصرّ على مبلغ فوق السقف ⇒ لا ترسل؛ اقترح تقديم الجزء الموافق للسياسة فقط.
@@ -2653,7 +2673,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-13T14:36:56</t>
+          <t>2026-08-13T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2736,6 +2756,11 @@
 # مهارة: طلب صلاحية نظام
 ## الغرض
 طلب منح أو ترقية صلاحية على نظام مؤسسي، مع فرض مبدأ **الحد الأدنى من الصلاحيات** وفحص الأهلية الوظيفية قبل وصول الطلب لسلسلة الاعتماد الأمنية.
+## أسلوب الجمع: خيارات لا أسئلة مفتوحة
+- النظام: اعرض الأنظمة من get_system_catalog كخيارات بأسمائها العربية (مع درجة الحساسية بين قوسين).
+- المستوى: «قراءة (read)»، «إدخال وتعديل (write)»، «إدارة (admin — مؤقتة إلزاميًا)».
+- المدة: «دائمة»، «٣ أشهر»، «شهر»، «مدة أخرى…» — واذكر أن المؤقتة تُفضَّل.
+- تحقق الأهلية أولًا: إن كان دور الموظف خارج allowed_roles فلا تعرض النظام كخيار أصلًا، أو اعرضه معطّلًا مع سبب الرفض.
 ## الحقول المطلوبة
 | الحقل | القيم | ملاحظات |
 |---|---|---|
@@ -2756,6 +2781,8 @@
 3. اجمع الحقول وطبّق القواعد أعلاه بالترتيب.
 4. اعرض **بطاقة معاينة**: النظام، المستوى، المدة، المبرر، سلسلة الاعتماد الكاملة، وتحذير الحساسية إن وجد.
 5. بعد تأكيد الموظف: submit_transaction.
+## تقرير المعتمِد (إلزامي)
+قبل submit_transaction أدرج في payload حقل `approver_report`: «الموظف: الاسم — الرقم — الإدارة — الدرجة | الطلب: سطر واحد | التحقق: كل فحص أجريته ونتيجته | التوصية: اعتماد / اعتماد مع ملاحظة / يحتاج تدقيقًا — مع السبب». لا تدرج إلا ما تحققت منه فعلًا عبر الخدمات.
 ## التصعيد والاستثناءات
 - طلب «مستعجل جدًا» لتجاوز السلسلة ⇒ ارفض التجاوز واشرح أن السلسلة قصيرة (sla 24 ساعة).
 - نظام غير موجود في الدليل ⇒ needs_attention لفريق التقنية؛ لا تخترع أنظمة.
@@ -2771,7 +2798,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-13T14:36:56</t>
+          <t>2026-08-13T15:04:41</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2917,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-13T14:36:56</t>
+          <t>2026-08-13T15:04:41</t>
         </is>
       </c>
     </row>

--- a/data/seeds/munjiz-registry-seed.xlsx
+++ b/data/seeds/munjiz-registry-seed.xlsx
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11T15:04:41</t>
+          <t>2026-01-04T13:00:00Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"leave_type": "annual", "start_date": "2026-08-20", "end_date": "2026-08-24", "working_days": 3, "reason": "إجازة عائلية"}</t>
+          <t>{"leave_type": "annual", "start_date": "2026-01-12", "end_date": "2026-01-16", "working_days": 3, "reason": "إجازة عائلية"}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-12T15:04:41</t>
+          <t>2026-01-05T03:00:00Z</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12T09:04:41</t>
+          <t>2026-01-04T03:00:00Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"category": "training", "amount_aed": 850, "expense_date": "2026-08-07", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741", "approver_report": "الموظف: راشد الكتبي (تجريبي) — EMP-1004 — الاتصال المؤسسي — G8 | الطلب: استرداد 850 درهمًا رسوم ورشة تدريبية معتمدة بتاريخ قريب | التحقق: الفئة training سقفها الشهري 2000 درهم والمصروف السابق 0 — المبلغ ضمن السقف؛ رقم الإيصال RCPT-7741 مرفق كما تشترط السياسة فوق 100 درهم؛ التاريخ ضمن مهلة 60 يومًا | التوصية: اعتماد — الطلب مستوفٍ لجميع شروط السياسة."}</t>
+          <t>{"category": "training", "amount_aed": 850, "expense_date": "2025-12-30", "description": "رسوم ورشة تدريبية معتمدة", "receipt_ref": "RCPT-7741", "approver_report": "الموظف: راشد الكتبي (تجريبي) — EMP-1004 — الاتصال المؤسسي — G8 | الطلب: استرداد 850 درهمًا رسوم ورشة تدريبية معتمدة بتاريخ قريب | التحقق: الفئة training سقفها الشهري 2000 درهم والمصروف السابق 0 — المبلغ ضمن السقف؛ رقم الإيصال RCPT-7741 مرفق كما تشترط السياسة فوق 100 درهم؛ التاريخ ضمن مهلة 60 يومًا | التوصية: اعتماد — الطلب مستوفٍ لجميع شروط السياسة."}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-12T09:04:41</t>
+          <t>2026-01-04T03:00:00Z</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T15:04:41</t>
+          <t>2025-12-27T09:00:00Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-04T15:04:41</t>
+          <t>2025-12-27T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11T15:04:41</t>
+          <t>2026-01-04T12:59:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11T15:04:41</t>
+          <t>2026-01-04T13:00:00Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-24T15:04:41</t>
+          <t>2025-12-16T09:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24T15:04:41</t>
+          <t>2025-12-16T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-07T15:04:41</t>
+          <t>2025-12-30T09:00:00Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-07T15:04:41</t>
+          <t>2025-12-30T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-10T15:04:41</t>
+          <t>2026-01-02T09:00:00Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-10T15:04:41</t>
+          <t>2026-01-02T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:04:41</t>
+          <t>2026-01-05T04:00:00Z</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-13T10:04:41</t>
+          <t>2026-01-05T04:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-13T15:04:41</t>
+          <t>2026-01-05T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-13T15:04:41</t>
+          <t>2026-01-05T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-13T15:04:41</t>
+          <t>2026-01-05T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-13T15:04:41</t>
+          <t>2026-01-05T09:00:00Z</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-13T15:04:41</t>
+          <t>2026-01-05T09:00:00Z</t>
         </is>
       </c>
     </row>
